--- a/www/download/IND.emp.s.un.rpPE.xlsx
+++ b/www/download/IND.emp.s.un.rpPE.xlsx
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Petrovic</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>8.289</t>
+          <t>8288820</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.355</t>
+          <t>8354550</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>8.477</t>
+          <t>8476975</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>8.642</t>
+          <t>8641615</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>8.834</t>
+          <t>8833540</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>9.012</t>
+          <t>9012162.372977</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>9.13</t>
+          <t>9129560.80671462</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>9.367</t>
+          <t>9366902.84863187</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>9.519</t>
+          <t>9518830.40875171</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>9.774</t>
+          <t>9773745.40717266</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>10.029</t>
+          <t>10028875.8637305</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>10.288</t>
+          <t>10288121.0794038</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>10.558</t>
+          <t>10558402.0486772</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>10.861</t>
+          <t>10861212.6850247</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>10.935</t>
+          <t>10935420.7530093</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3.717</t>
+          <t>3717450</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>3.746</t>
+          <t>3745607</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>3.773</t>
+          <t>3773250</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>3.813</t>
+          <t>3812808</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>3.881</t>
+          <t>3880567</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3.931</t>
+          <t>3931132</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3.959</t>
+          <t>3958982</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>3.959</t>
+          <t>3959496</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>3.971</t>
+          <t>3971206</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>3.986</t>
+          <t>3986006</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>4.031</t>
+          <t>4031292</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>4.09</t>
+          <t>4090488</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>4.161</t>
+          <t>4160866</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>4300196.26714888</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>4.213</t>
+          <t>4212848.58615411</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3.867</t>
+          <t>3867180</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3.878</t>
+          <t>3877602</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>3.904</t>
+          <t>3904154</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>3.973</t>
+          <t>3972758</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>4.028</t>
+          <t>4027605</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>4.109</t>
+          <t>4108957</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4.165</t>
+          <t>4165431</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>4.159</t>
+          <t>4158946</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>4.16</t>
+          <t>4160432</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>4.199</t>
+          <t>4198741</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>4.258</t>
+          <t>4258009</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>4.308</t>
+          <t>4308495</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>4.378</t>
+          <t>4378108</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>4.45</t>
+          <t>4449893.32227832</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>4.438</t>
+          <t>4437555.55062773</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>3.519</t>
+          <t>3518768.77238457</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3.614</t>
+          <t>3613757.57272251</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3500495.20410063</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>3.472</t>
+          <t>3472496.63818831</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3.312</t>
+          <t>3312407.71670649</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>3.239</t>
+          <t>3239300</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3.215</t>
+          <t>3214800</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>3.222</t>
+          <t>3222200</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>3.317</t>
+          <t>3317400</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>3.404</t>
+          <t>3403500</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>3.495</t>
+          <t>3495200</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>3.612</t>
+          <t>3612000</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>3.727</t>
+          <t>3726600</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>3759606.5276488</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>3.74</t>
+          <t>3739755.21450808</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>73.545</t>
+          <t>73545221.6136996</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>71.986</t>
+          <t>71985645.4011104</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>73.128</t>
+          <t>73128236.0519808</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>72.745</t>
+          <t>72744860.8372439</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>76.641</t>
+          <t>76641008.2837895</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>78.972</t>
+          <t>78972347</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>79.544</t>
+          <t>79544414</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>82.629</t>
+          <t>82629067</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>84.035</t>
+          <t>84034981</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>88.252</t>
+          <t>88252473</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>90.906</t>
+          <t>90905673</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>93.247</t>
+          <t>93246963</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>94.714</t>
+          <t>94713909</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>96.233</t>
+          <t>96232609</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>96.647</t>
+          <t>96647139</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>13.593</t>
+          <t>13593006.8730362</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>13.739</t>
+          <t>13739222.1632323</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>14.028</t>
+          <t>14027669.99811</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>14.345</t>
+          <t>14345414.99821</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>14.72</t>
+          <t>14719774.99802</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>15.048</t>
+          <t>15048149.99801</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>15.199</t>
+          <t>15199154.99804</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>15.568</t>
+          <t>15568199.99803</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>15.902</t>
+          <t>15901974.99803</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>16.166</t>
+          <t>16165969.99803</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>16.405</t>
+          <t>16405414.99804</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>16.677</t>
+          <t>16676749.99804</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>17.047</t>
+          <t>17046849.99804</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>17.486</t>
+          <t>17485670.859599</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>16.875</t>
+          <t>16875446.8452208</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>680.65</t>
+          <t>680650000</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>689.5</t>
+          <t>689500000</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>698.2</t>
+          <t>698200000</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>706.37</t>
+          <t>706370000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>713.94</t>
+          <t>713940000</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>720.85</t>
+          <t>720850000</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>730.25</t>
+          <t>730250000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>737.4</t>
+          <t>737400000</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>744.32</t>
+          <t>744320000</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>752</t>
+          <t>7.52e+08</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>758.25</t>
+          <t>758250000</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>764</t>
+          <t>7.64e+08</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>769.9</t>
+          <t>769900000</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>774.8</t>
+          <t>774800000</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>779.95</t>
+          <t>779950000</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.296</t>
+          <t>296100</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.298</t>
+          <t>297700</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>299500</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>0.304</t>
+          <t>304100</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>309800</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.315</t>
+          <t>314800</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.322</t>
+          <t>321900</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.328</t>
+          <t>328300</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>0.341</t>
+          <t>340800</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0.353</t>
+          <t>353300</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>0.366</t>
+          <t>366400</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>0.372</t>
+          <t>372400</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>0.384</t>
+          <t>384500</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>0.391</t>
+          <t>391166.670871672</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>0.393</t>
+          <t>392612.725033373</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>5.148</t>
+          <t>5148229</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>5.195</t>
+          <t>5195164</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>5.205</t>
+          <t>5204858</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>5.125</t>
+          <t>5124530</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>4.949</t>
+          <t>4949350</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>4.94</t>
+          <t>4940463</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>4.963</t>
+          <t>4962963</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>4.991</t>
+          <t>4990747</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>4.923</t>
+          <t>4923446</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>4.94</t>
+          <t>4940371</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>4.992</t>
+          <t>4991618</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>5.088</t>
+          <t>5088340</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>5.224</t>
+          <t>5223840</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>5.349</t>
+          <t>5348855.37841137</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>5.232</t>
+          <t>5231900.73131227</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>37.601</t>
+          <t>37601000</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>37.498</t>
+          <t>37498000</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>37.463</t>
+          <t>37463000</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>37.911</t>
+          <t>37911000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>38.424</t>
+          <t>38424000</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>39.144</t>
+          <t>39144000</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>39.316</t>
+          <t>39316000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>39.096</t>
+          <t>39096000</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>38.726</t>
+          <t>38726000</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>38.88</t>
+          <t>38880000</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>38.835</t>
+          <t>38835000</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>39.075</t>
+          <t>39075000</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>39.724</t>
+          <t>39724000</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>40.45</t>
+          <t>40450357.994188</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>40.85</t>
+          <t>40849767.096668</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2.553</t>
+          <t>2552724</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2.584</t>
+          <t>2584116</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2.628</t>
+          <t>2627783</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2.668</t>
+          <t>2668106</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2.694</t>
+          <t>2693717</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2.712</t>
+          <t>2712496</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.742</t>
+          <t>2742475</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.746</t>
+          <t>2745960</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2.714</t>
+          <t>2713539</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2.698</t>
+          <t>2697642</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2.727</t>
+          <t>2726912</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2.783</t>
+          <t>2783454</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>2.861</t>
+          <t>2860799</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2.907</t>
+          <t>2907479.77406196</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2.856</t>
+          <t>2856442.13464624</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>13.569</t>
+          <t>13569300.9999473</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>13.796</t>
+          <t>13795999.000192</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>14.293</t>
+          <t>14293301.0001657</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>14.932</t>
+          <t>14931999.9999472</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>15.617</t>
+          <t>15617098.9999302</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>16.412</t>
+          <t>16411500</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>16.931</t>
+          <t>16930600</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>17.338</t>
+          <t>17337600</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>17.878</t>
+          <t>17877600</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>18.51</t>
+          <t>18509800</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>19.267</t>
+          <t>19267300</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>20.022</t>
+          <t>20022000</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>20.628</t>
+          <t>20628500</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>20.576</t>
+          <t>20576317.1803866</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>19.258</t>
+          <t>19257725.8112927</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.633</t>
+          <t>633300</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0.619</t>
+          <t>619300</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.617</t>
+          <t>617200</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>0.606</t>
+          <t>606300</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0.579</t>
+          <t>579200</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.573</t>
+          <t>572500</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0.578</t>
+          <t>577699.999832412</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>0.585</t>
+          <t>585300</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>0.594</t>
+          <t>594000</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0.595</t>
+          <t>595300.000127613</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>0.608</t>
+          <t>607700</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>0.646</t>
+          <t>646000</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>0.656</t>
+          <t>655600.000094429</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>660424.806154005</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>0.614</t>
+          <t>614162.221545645</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2.053</t>
+          <t>2052700</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2.082</t>
+          <t>2081800</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2.153</t>
+          <t>2152900</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2.193</t>
+          <t>2192700</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2.247</t>
+          <t>2247200</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2.293</t>
+          <t>2293400</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2.324</t>
+          <t>2324200</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2.346</t>
+          <t>2346200</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2.348</t>
+          <t>2347600</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2.357</t>
+          <t>2356900</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2.389</t>
+          <t>2389200</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2.433</t>
+          <t>2433200</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>2.486</t>
+          <t>2486100</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2.541</t>
+          <t>2540816.41732835</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2.468</t>
+          <t>2468383.78660693</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>22.694</t>
+          <t>22694100</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>22.78</t>
+          <t>22779700</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>22.879</t>
+          <t>22879400</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>23.227</t>
+          <t>23227200</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>23.696</t>
+          <t>23696500</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>24.332</t>
+          <t>24331900</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>24.765</t>
+          <t>24764500</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>24.919</t>
+          <t>24918800</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>24950200</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>24.977</t>
+          <t>24977000</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>25.115</t>
+          <t>25115300</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>25.362</t>
+          <t>25362100</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>25.729</t>
+          <t>25729400</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>25.945</t>
+          <t>25944882.8155248</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>25.522</t>
+          <t>25522261.9901433</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>27.913</t>
+          <t>27913387.7468886</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>28.164</t>
+          <t>28163684.9898958</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>28.63</t>
+          <t>28630138.8273842</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>28.88</t>
+          <t>28879660.1410479</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>29.267</t>
+          <t>29267235.4487518</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>29.617</t>
+          <t>29617096.5365194</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>29.925</t>
+          <t>29924752.1919734</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>30.106</t>
+          <t>30105879.5400161</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>30.408</t>
+          <t>30408163.3871446</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>30.703</t>
+          <t>30703397.31174</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>31.09</t>
+          <t>31090257.8953786</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>31.398</t>
+          <t>31398264.8920847</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>31.602</t>
+          <t>31601986.058387</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>31.674</t>
+          <t>31673802.9339179</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>30.972</t>
+          <t>30972251.5790757</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>4.131</t>
+          <t>4131219</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>4.115</t>
+          <t>4114854</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>4.092</t>
+          <t>4092138</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>4.261</t>
+          <t>4261223</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>4.262</t>
+          <t>4261966</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>4.255</t>
+          <t>4255111</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>4.261</t>
+          <t>4260548</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>4.356</t>
+          <t>4356484</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>4.408</t>
+          <t>4408021</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>4.514</t>
+          <t>4514447</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>4.551</t>
+          <t>4550601</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>4.701</t>
+          <t>4700825</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>4.783</t>
+          <t>4782684</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>4.947</t>
+          <t>4946734.91482196</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>5.035</t>
+          <t>5034791.95208993</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>4.025</t>
+          <t>4025461</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>4030099</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>4.026</t>
+          <t>4026318</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>4.097</t>
+          <t>4096782</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>4.208</t>
+          <t>4208414</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>4250367</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>4.232</t>
+          <t>4231638</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>4.224</t>
+          <t>4223693</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>4.227</t>
+          <t>4226739</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>4.166</t>
+          <t>4166006</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>4.156</t>
+          <t>4155867</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>4.182</t>
+          <t>4181597</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>4.169</t>
+          <t>4169042</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>4.069</t>
+          <t>4068691.46704218</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>3.958</t>
+          <t>3957946.60261327</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>87.271</t>
+          <t>87271197</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>88.91</t>
+          <t>88910252.0210243</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>90.204</t>
+          <t>90203589.8353118</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>90.827</t>
+          <t>90826739.1939587</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>92.114</t>
+          <t>92114360.1162204</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>93.321</t>
+          <t>93320951</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>93.437</t>
+          <t>93437042.6679519</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>93.655</t>
+          <t>93654956.6096022</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>94.323</t>
+          <t>94322550.2018638</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>94.695</t>
+          <t>94695473.4336958</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>95.464</t>
+          <t>95463852</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>97.88</t>
+          <t>97879767.1210441</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>103.349</t>
+          <t>103349377.053964</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>105.753</t>
+          <t>105753227.039894</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>108.203</t>
+          <t>108202785.041088</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>380.787</t>
+          <t>380787429.414916</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>393.501</t>
+          <t>393500838.072331</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>397.971</t>
+          <t>397970756.609609</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>401.547</t>
+          <t>401546875.716261</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>398.413</t>
+          <t>398412827</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>416.883</t>
+          <t>416883259.227144</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>432.376</t>
+          <t>432375751.095812</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>424.206</t>
+          <t>424205792.732751</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>449.023</t>
+          <t>449023250.747477</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>457.9</t>
+          <t>457899624</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>469.777</t>
+          <t>469777231.09542</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>471.768</t>
+          <t>471767957.605752</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>460.23</t>
+          <t>460230081</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>463.379</t>
+          <t>463378669.072472</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>465.828</t>
+          <t>465827675.054621</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1.285</t>
+          <t>1285146.05664965</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1.331</t>
+          <t>1331163</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.405</t>
+          <t>1405489</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1.526</t>
+          <t>1526234</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>1.622</t>
+          <t>1621650</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>1.697</t>
+          <t>1697054</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1.748</t>
+          <t>1748052</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>1.779</t>
+          <t>1779225</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>1.814</t>
+          <t>1814490</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>1.871</t>
+          <t>1870606</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>1.962</t>
+          <t>1962375</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>2.048</t>
+          <t>2047601</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>2.123</t>
+          <t>2123002</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2.177</t>
+          <t>2176856.4465005</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2.002</t>
+          <t>2001673.25116501</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>21.841</t>
+          <t>21841200</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>21.966</t>
+          <t>21966000</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>22.035</t>
+          <t>22034700</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>22.253</t>
+          <t>22252600</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>22.494</t>
+          <t>22493900</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>22.93</t>
+          <t>22930100</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>23.393</t>
+          <t>23393105.5806433</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>23.793</t>
+          <t>23793100</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>24.15</t>
+          <t>24149600</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>24.256</t>
+          <t>24256100</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>24.396</t>
+          <t>24395800</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>24.874</t>
+          <t>24874100</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>25.188</t>
+          <t>25187900</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>25.278</t>
+          <t>25277735.5571035</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>25.079</t>
+          <t>25078809.506742</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>66.858</t>
+          <t>66857749.2126289</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>66.907</t>
+          <t>66906725.9645875</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>67.374</t>
+          <t>67373676.3052891</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>66.58</t>
+          <t>66579630.0285745</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>65.664</t>
+          <t>65663597.6201838</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>65.253</t>
+          <t>65252580.5313763</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>64.76</t>
+          <t>64759579.8985275</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>63.748</t>
+          <t>63747574.9491338</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>63.537</t>
+          <t>63536567.4245277</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>63.677</t>
+          <t>63676553.3755598</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>63.917</t>
+          <t>63916550.6509646</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>64.197</t>
+          <t>64197437.9942584</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>64.438</t>
+          <t>64438263.1188283</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>63.045</t>
+          <t>63045011.7904479</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>58.129</t>
+          <t>58129224.001234</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>20.398</t>
+          <t>20398000</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>20.837</t>
+          <t>20837000</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>21.201</t>
+          <t>21201000</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>19.918</t>
+          <t>19918000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>20.277</t>
+          <t>20277000</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>21.136</t>
+          <t>21136000</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>21.557</t>
+          <t>21557000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>22.152</t>
+          <t>22152000</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>22.117</t>
+          <t>22117000</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>22.534</t>
+          <t>22534000</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>22.83</t>
+          <t>22830000</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>23.133</t>
+          <t>23133000</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>23.418</t>
+          <t>23418000</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>23.561</t>
+          <t>23560890.1689708</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>23.49</t>
+          <t>23489944.7004608</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1480200</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1.493</t>
+          <t>1493500</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.502</t>
+          <t>1502500</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1490400</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>1.457</t>
+          <t>1457200</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>1.399</t>
+          <t>1399200</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1.346</t>
+          <t>1345900</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>1.395</t>
+          <t>1394900</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>1.426</t>
+          <t>1425900</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>1.426</t>
+          <t>1425500</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>1.461</t>
+          <t>1460700</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>1.488</t>
+          <t>1487600</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>1.529</t>
+          <t>1528900</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>1.531</t>
+          <t>1530742.48708814</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>1.443</t>
+          <t>1442881.941105</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.216</t>
+          <t>215500</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.221</t>
+          <t>221300</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.228</t>
+          <t>227900</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.238</t>
+          <t>238100</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.264</t>
+          <t>263700</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.278</t>
+          <t>278100</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.288</t>
+          <t>287500</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.293</t>
+          <t>292700</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.299</t>
+          <t>299300</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.308</t>
+          <t>308100</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.319</t>
+          <t>318900</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>333000</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.371</t>
+          <t>370678.084209208</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>379928.384478628</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>969735.662321586</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>0.951</t>
+          <t>951270.049238141</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0.993</t>
+          <t>992998.054427078</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>989890.204352882</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>0.972</t>
+          <t>972383.807901089</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>0.941</t>
+          <t>941400</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.953</t>
+          <t>953100</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.981</t>
+          <t>980925.625</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1000100</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>1.012</t>
+          <t>1012467.65402844</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>1.032</t>
+          <t>1032012.20379147</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>1.079</t>
+          <t>1079300</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>1.118</t>
+          <t>1117700</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>1.121</t>
+          <t>1120558.35643642</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>0.955</t>
+          <t>955265.981536636</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>33.128</t>
+          <t>33127869.0257056</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>34.307</t>
+          <t>34306518.3426035</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>35.189</t>
+          <t>35189306.1721399</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>36.555</t>
+          <t>36554940.9240297</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>37.969</t>
+          <t>37969392.3967439</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>39.226</t>
+          <t>39225534.7394746</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>40.103</t>
+          <t>40103380.1659265</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>40.958</t>
+          <t>40958074.5334656</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>41.656</t>
+          <t>41655918.7881667</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>43.032</t>
+          <t>43032457.7788705</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>43.702</t>
+          <t>43701833.2099097</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>45.269</t>
+          <t>45268677.2097568</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>46.08</t>
+          <t>46080116.0593819</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>49.694</t>
+          <t>49694372.6290224</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>49.056</t>
+          <t>49055599.7627067</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>138874.446687167</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>139488.262001645</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>140044.246782362</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>0.142</t>
+          <t>141987.657087953</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>0.144</t>
+          <t>143908.239551269</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>0.146</t>
+          <t>145532.567350409</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.149</t>
+          <t>148518.699858705</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>151325.446256559</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>150581.137128626</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0.149</t>
+          <t>148818.629624851</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>150919.65916683</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>0.154</t>
+          <t>154191.416391832</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>0.159</t>
+          <t>159111.861238722</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>0.164</t>
+          <t>163839.80861896</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>0.162</t>
+          <t>162466.36194054</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>7.155</t>
+          <t>7154972</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>7.315</t>
+          <t>7314819</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>7.541</t>
+          <t>7541382</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>7.738</t>
+          <t>7738203</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>7.937</t>
+          <t>7936943</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>8.115</t>
+          <t>8115485</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>8.282</t>
+          <t>8282403</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>8.324</t>
+          <t>8323918</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>8.283</t>
+          <t>8283124</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>8.211</t>
+          <t>8211304</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>8.252</t>
+          <t>8251595</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>8.392</t>
+          <t>8392348</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>8.607</t>
+          <t>8606582</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>8.738</t>
+          <t>8737563.61515372</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>8.694</t>
+          <t>8693514.58520918</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>14.735</t>
+          <t>14735200</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>15.021</t>
+          <t>15020600</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>15.439</t>
+          <t>15438700</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>15.8</t>
+          <t>15800400</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>15.375</t>
+          <t>15375000</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>15.018</t>
+          <t>15017500</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>14.195</t>
+          <t>14194800</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>13.766</t>
+          <t>13766300</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>13.606</t>
+          <t>13606100</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>13.773</t>
+          <t>13773300</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>14.075</t>
+          <t>14074500</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>14.53</t>
+          <t>14529900</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>15.174</t>
+          <t>15174200</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>15.784</t>
+          <t>15783645.889573</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>15.786</t>
+          <t>15786155.3712382</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>4.531</t>
+          <t>4530800</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>4.607</t>
+          <t>4607000</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>4.728</t>
+          <t>4727600</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>4860200</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>4.927</t>
+          <t>4927000</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>5030000</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>5.121</t>
+          <t>5121200</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>5.151</t>
+          <t>5151300</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>5.122</t>
+          <t>5122000</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>5.117</t>
+          <t>5116800</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>5100000</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>5.201</t>
+          <t>5200900</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>5.198</t>
+          <t>5197884.78617838</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>5.218</t>
+          <t>5217616.27334019</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>5.053</t>
+          <t>5053215.15007551</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>9.503</t>
+          <t>9503080.13946449</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>9.379</t>
+          <t>9378883.34754797</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>9.023</t>
+          <t>9022592.28144989</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>8.813</t>
+          <t>8812501.66311301</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>10.855</t>
+          <t>10855400</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>10.771</t>
+          <t>10771400</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>10.657</t>
+          <t>10657400</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>9.574</t>
+          <t>9574000</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>9.569</t>
+          <t>9569500</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>9410200</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>9.267</t>
+          <t>9267300</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>9.331</t>
+          <t>9331000</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>9.365</t>
+          <t>9364900</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>9.366</t>
+          <t>9366300</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>9.212</t>
+          <t>9211994.64560414</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>75.064</t>
+          <t>75064020.4105068</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>72.952</t>
+          <t>72952323.1444098</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>72.752</t>
+          <t>72751632.044012</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>70.679</t>
+          <t>70678642.9778868</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>72.536</t>
+          <t>72536304.6533051</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>73.726</t>
+          <t>73725622.6407169</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>74.727</t>
+          <t>74726901.7613503</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>74.928</t>
+          <t>74927528.6053486</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>75.796</t>
+          <t>75795783.2238575</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>76.274</t>
+          <t>76274192.8802783</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>76.903</t>
+          <t>76903373.2930301</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>77.376</t>
+          <t>77376240.0225884</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>78.352</t>
+          <t>78351850.9170373</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>78.688</t>
+          <t>78687685.7840791</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>75.717</t>
+          <t>75717000</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2.107</t>
+          <t>2107194</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2.151</t>
+          <t>2151114</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2.129</t>
+          <t>2128906</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2.119</t>
+          <t>2118874</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2.065</t>
+          <t>2065183</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2.025</t>
+          <t>2024843</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2.037</t>
+          <t>2036513</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2.038</t>
+          <t>2038414</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2060469</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>2.056</t>
+          <t>2055727</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2.089</t>
+          <t>2088913</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>2.132</t>
+          <t>2132389</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>2.177</t>
+          <t>2176971</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>2.262</t>
+          <t>2262293.83564775</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>2.251</t>
+          <t>2251181.62202833</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>0.918</t>
+          <t>918099</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>899514</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0.883</t>
+          <t>882596</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>0.881</t>
+          <t>881002</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>0.893</t>
+          <t>893143</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>0.905</t>
+          <t>904705</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.909</t>
+          <t>908909</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.923</t>
+          <t>922830</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>0.919</t>
+          <t>919233</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0.922</t>
+          <t>922090</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>920313</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>0.934</t>
+          <t>934160</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>0.962</t>
+          <t>962261</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>0.994</t>
+          <t>994232.219132951</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>0.974</t>
+          <t>973825.841177403</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>4.129</t>
+          <t>4128899.99999584</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>4.096</t>
+          <t>4095799.9999959</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>4.043</t>
+          <t>4043200</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>4.111</t>
+          <t>4111400</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>4.198</t>
+          <t>4197700.00000615</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>4.301</t>
+          <t>4300700.00000532</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>4.391</t>
+          <t>4391200</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>4.393</t>
+          <t>4393300.00000522</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>4.368</t>
+          <t>4367900</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>4.337</t>
+          <t>4337400</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>4.349</t>
+          <t>4348900</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>4.423</t>
+          <t>4422500</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>4.524</t>
+          <t>4524300</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>4.542</t>
+          <t>4541646.26335567</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>4.425</t>
+          <t>4424861.28133468</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>20.586</t>
+          <t>20586426.4895193</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>21.195</t>
+          <t>21194652.7011088</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>21.204</t>
+          <t>21204337.5465736</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>21.779</t>
+          <t>21778920.5046377</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>22.048</t>
+          <t>22048000</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>21.58</t>
+          <t>21580000</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>21.524</t>
+          <t>21524000</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>21.354</t>
+          <t>21354000</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>21.147</t>
+          <t>21147000</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>21.732</t>
+          <t>21732000</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>21.956</t>
+          <t>21956000</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>21.093</t>
+          <t>21092505.5053513</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>20.738</t>
+          <t>20738197.1165437</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>21.194</t>
+          <t>21193800.1698674</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>21.275</t>
+          <t>21275000</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>9.368</t>
+          <t>9368000</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>9.275</t>
+          <t>9275000</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>9.39</t>
+          <t>9390000</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>9.425</t>
+          <t>9425000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>9.458</t>
+          <t>9458000</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>9.597</t>
+          <t>9597000</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>9.383</t>
+          <t>9383000</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>9.454</t>
+          <t>9454000</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>9.574</t>
+          <t>9574000</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>9.784</t>
+          <t>9784000</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>9.943</t>
+          <t>9943000</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>10.113</t>
+          <t>10113000</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>10.292</t>
+          <t>10292000</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>10.404</t>
+          <t>10404000</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>10.279</t>
+          <t>10279000</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>133.979</t>
+          <t>133979321.123271</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>136.023</t>
+          <t>136022925.92767</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>138.548</t>
+          <t>138547833.030053</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>141.887</t>
+          <t>141887415.074678</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>144.534</t>
+          <t>144534413.329251</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>147.717</t>
+          <t>147716677.936947</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>146.818</t>
+          <t>146817829.339657</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>145.399</t>
+          <t>145399036.924174</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>145.189</t>
+          <t>145189036.081327</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>146.865</t>
+          <t>146864998.439847</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>148.903</t>
+          <t>148903330.424206</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>151.319</t>
+          <t>151319391.572917</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>152.567</t>
+          <t>152567147.548354</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>151.743</t>
+          <t>151742790.734829</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>145.345</t>
+          <t>145344828.726105</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>856.406</t>
+          <t>856406416.7</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>877.09</t>
+          <t>877089703.9</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>896.559</t>
+          <t>896558927.5</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>911.591</t>
+          <t>911591136.6</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>926.097</t>
+          <t>926097036</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>955.308</t>
+          <t>955308488.8</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>983.772</t>
+          <t>983772057.8</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>998.606</t>
+          <t>998605592.9</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>1035.462</t>
+          <t>1035462227</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>1066.542</t>
+          <t>1066541600</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>1095.297</t>
+          <t>1095296771</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>1124.55</t>
+          <t>1124550408</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>1146.413</t>
+          <t>1146412933</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>1174.341</t>
+          <t>1174341498</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>1192.928</t>
+          <t>1192927772</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2660.653</t>
+          <t>2660653299.68762</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2706.543</t>
+          <t>2706543192.85967</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2747.777</t>
+          <t>2747776983.70739</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2779.313</t>
+          <t>2779312648.15922</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2813.91</t>
+          <t>2813909726.61036</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2881.293</t>
+          <t>2881293416.35052</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>2937.735</t>
+          <t>2937735363.00629</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>2954.355</t>
+          <t>2954355370.71242</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>3027.326</t>
+          <t>3027325963.39827</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>3086.349</t>
+          <t>3086349111.90897</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>3143.524</t>
+          <t>3143523990.29364</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>3193.889</t>
+          <t>3193889272.41759</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>3225.066</t>
+          <t>3225065864.56672</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>3270.744</t>
+          <t>3270744373.24015</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>3280.621</t>
+          <t>3280621015.7904</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4339,7 +4344,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4351,7 +4356,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4363,7 +4368,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4375,7 +4380,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4387,7 +4392,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4399,7 +4404,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4411,7 +4416,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4423,7 +4428,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4462,12 +4467,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -4504,6 +4514,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Petrovic</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpPE</t>
